--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/нет продаж.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/нет продаж.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E0E00A-5444-4BA4-849A-D5EDCE39CF26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0A2549-C3B0-4190-B6FE-989DE6EBDDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -91,6 +91,24 @@
   </si>
   <si>
     <t>Сыч/Прод Коровино Российский Оригин 50% ВЕС НОВАЯ (3,5 кг)  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Плавленый Сыр колбасный копченый 40% СТМ"ПапаМожет"400гр  Останкино</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Сыр Папа Может "Гауда Голд" 45% (-2,5 кг брус) (6 шт)  Останкино</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС (3,5 кг брус) СЗМЖ  Останкино</t>
   </si>
 </sst>
 </file>
@@ -111,11 +129,15 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="90.7109375" bestFit="1" customWidth="1"/>
@@ -698,6 +720,233 @@
         <v>110.39700000000001</v>
       </c>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
+        <v>140</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <v>80.346000000000004</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2">
+        <v>80.346000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2">
+        <v>-2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>125.246</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2">
+        <v>3.476</v>
+      </c>
+      <c r="F22" s="2">
+        <v>121.77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>36.363999999999997</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2">
+        <v>36.363999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2">
+        <v>149</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
+        <v>17.07</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
+        <v>53.936</v>
+      </c>
+      <c r="D32" s="2">
+        <v>82</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2">
+        <v>308.97699999999998</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2">
+        <v>9.9039999999999999</v>
+      </c>
+      <c r="F33" s="2">
+        <v>299.07299999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
